--- a/output/global_jobs.xlsx
+++ b/output/global_jobs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:Z51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,35 +511,50 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>seniority_level</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>posted_date</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>keyword_matches</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>score_reasons</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>description_snippet</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>has_keyword_match</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dedupe_key</t>
         </is>
@@ -548,17 +563,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Head of Global Finance and Accounting Operations</t>
+          <t>Vice President - Export &amp; Agency Finance, Execution Control - Services</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>London United Kingdom</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -582,12 +597,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -605,57 +620,64 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>200-300k</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>4202 BFin - FinOps (SDC)</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Ejecutivo</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7334756</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="b">
-        <v>1</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7334756 | stripe | head of global finance and accounting operations</t>
+          <t>match de keywords: finance | seniority alta | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>https://citi.wd5.myworkdayjobs.com/2/job/London--United-Kingdom/Vice-President---Export---Agency-Finance--Execution-Control---Services_26936717</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>https://citi.wd5.myworkdayjobs.com/2</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>https://citi.wd5.myworkdayjobs.com/2/job/london--united-kingdom/vice-president---export---agency-finance--execution-control---services_26936717 | citi | vice president - export &amp; agency finance, execution control - services</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Senior Manager, Finance Transformation</t>
+          <t>Field Business Partner - Theater Director (Remote, AUS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote - USA</t>
+          <t>4 Locations</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -664,7 +686,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -679,12 +701,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -702,66 +724,73 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>200-300k</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Finance &amp; Accounting</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>finance, finance transformation</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Ejecutivo</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>https://www.coinbase.com/careers/positions/7430307?gh_jid=7430307</t>
+          <t>business partner</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/coinbase</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="b">
-        <v>1</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>https://www.coinbase.com/careers/positions/7430307?gh_jid=7430307 | coinbase | senior manager, finance transformation</t>
+          <t>match de keywords: business partner | seniority alta | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>https://crowdstrike.wd5.myworkdayjobs.com/crowdstrikecareers/job/Australia---Remote-NW/Sr-Manager--Theater-Business-Partner--Remote--AUS-_R25382</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>https://crowdstrike.wd5.myworkdayjobs.com/crowdstrikecareers</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>https://crowdstrike.wd5.myworkdayjobs.com/crowdstrikecareers/job/australia---remote-nw/sr-manager--theater-business-partner--remote--aus-_r25382 | crowdstrike | field business partner - theater director (remote, aus)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Senior Product Manager, Enterprise Applications - Finance Systems</t>
+          <t>Finance Director, Barnard Castle</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote - USA</t>
+          <t>UK - County Durham - Barnard Castle</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>remote</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -776,17 +805,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -796,69 +825,76 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>200-300k</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Enterprise Applications</t>
-        </is>
-      </c>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>finance</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Ejecutivo</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>https://www.coinbase.com/careers/positions/7404427?gh_jid=7404427</t>
+          <t>finance, finance director</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/coinbase</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="b">
-        <v>1</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>https://www.coinbase.com/careers/positions/7404427?gh_jid=7404427 | coinbase | senior product manager, enterprise applications - finance systems</t>
+          <t>match de keywords: finance, finance director | seniority alta | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>https://gsk.wd5.myworkdayjobs.com/GSKCareers/job/UK---County-Durham---Barnard-Castle/Finance-Director--Barnard-Castle_437362-1</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>https://gsk.wd5.myworkdayjobs.com/GSKCareers</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="Y4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>https://gsk.wd5.myworkdayjobs.com/gskcareers/job/uk---county-durham---barnard-castle/finance-director--barnard-castle_437362-1 | gsk | finance director, barnard castle</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Danaher</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Senior Finance Manager - Plant Controller - Ilfracombe</t>
+          <t>Senior Director, People Business Partner</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Braunton, United Kingdom</t>
+          <t>Remote, US</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -873,12 +909,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Life Sciences</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -893,56 +929,71 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>170-230k</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>People Business Partners</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>finance, finance manager, senior finance manager</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Ejecutivo</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://danaher.wd1.myworkdayjobs.com/en-US/DanaherJobs/job/Braunton-United-Kingdom/Senior-Finance-Manager---Plant-Controller---Ilfracombe_R1305356</t>
+          <t>business partner</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://danaher.wd1.myworkdayjobs.com/en-US/DanaherJobs</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="b">
-        <v>1</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>https://danaher.wd1.myworkdayjobs.com/en-us/danaherjobs/job/braunton-united-kingdom/senior-finance-manager---plant-controller---ilfracombe_r1305356 | danaher | senior finance manager - plant controller - ilfracombe</t>
+          <t>match de keywords: business partner | seniority alta | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8440520002</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/gitlab</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8440520002 | gitlab | senior director, people business partner</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Senior Manager – International Finance</t>
+          <t>Finance Director, DPS International Canada</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hyderabad (Office)</t>
+          <t>Markham, Ontario, Canada</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -951,7 +1002,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -976,7 +1027,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -986,65 +1037,76 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>170-240k</t>
-        </is>
-      </c>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>finance</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Ejecutivo</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://novartis.wd3.myworkdayjobs.com/Novartis_Careers/job/Hyderabad-Office/Senior-Manager---International-Finance_REQ-10072237</t>
+          <t>finance, finance director</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://novartis.wd3.myworkdayjobs.com/Novartis_Careers</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="b">
-        <v>1</v>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>https://novartis.wd3.myworkdayjobs.com/novartis_careers/job/hyderabad-office/senior-manager---international-finance_req-10072237 | novartis | senior manager – international finance</t>
+          <t>match de keywords: finance, finance director | seniority alta | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>https://jj.wd5.myworkdayjobs.com/JJ/job/Markham-Ontario-Canada/Finance-Director--DPS-International-Canada_R-061129-1</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>https://jj.wd5.myworkdayjobs.com/JJ</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>https://jj.wd5.myworkdayjobs.com/jj/job/markham-ontario-canada/finance-director--dps-international-canada_r-061129-1 | johnson &amp; johnson | finance director, dps international canada</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Johnson &amp; Johnson Mexico</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Finance Reconciliation Operations &amp; Strategy Associate</t>
+          <t>Finance Director, DPS International Canada</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote - Singapore</t>
+          <t>Markham, Ontario, Canada</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>remote</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1059,17 +1121,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workday</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>LATAM</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1082,66 +1144,73 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>200-300k</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Finance &amp; Accounting</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>finance</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Ejecutivo</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.coinbase.com/careers/positions/7602823?gh_jid=7602823</t>
+          <t>finance, finance director</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/coinbase</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="b">
-        <v>1</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>https://www.coinbase.com/careers/positions/7602823?gh_jid=7602823 | coinbase | finance reconciliation operations &amp; strategy associate</t>
+          <t>match de keywords: finance, finance director | seniority alta | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>https://jj.wd5.myworkdayjobs.com/JJ/job/Markham-Ontario-Canada/Finance-Director--DPS-International-Canada_R-061129-1</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>https://jj.wd5.myworkdayjobs.com/JJ</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="Y7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>https://jj.wd5.myworkdayjobs.com/jj/job/markham-ontario-canada/finance-director--dps-international-canada_r-061129-1 | johnson &amp; johnson mexico | finance director, dps international canada</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Financial Analyst, Corporate FP&amp;A</t>
+          <t>Strategic Finance Manager, International Public Sector</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote - USA</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>remote</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1161,7 +1230,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1179,57 +1248,68 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>200-300k</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Finance &amp; Accounting</t>
+          <t>CFO Team</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>fp&amp;a</t>
-        </is>
-      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.coinbase.com/careers/positions/7676111?gh_jid=7676111</t>
+          <t>finance, strategic finance, finance manager</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/coinbase</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="b">
-        <v>1</v>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>https://www.coinbase.com/careers/positions/7676111?gh_jid=7676111 | coinbase | financial analyst, corporate fp&amp;a</t>
+          <t>match fuerte de keywords: finance, strategic finance, finance manager | seniority media-alta | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4631613005</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/scaleai</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4631613005 | scale ai | strategic finance manager, international public sector</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Global Finance Master Data Senior Specialist</t>
+          <t>Head of Global Finance and Accounting Operations</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>INSURGENTES</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1238,7 +1318,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1253,17 +1333,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>workday</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1273,56 +1353,71 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>170-240k</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>4202 BFin - FinOps (SDC)</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Ejecutivo</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
         <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>https://novartis.wd3.myworkdayjobs.com/Novartis_Careers/job/INSURGENTES/Global-Finance-Master-Data-Senior-Specialist_REQ-10072223-1</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://novartis.wd3.myworkdayjobs.com/Novartis_Careers</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="b">
-        <v>1</v>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>https://novartis.wd3.myworkdayjobs.com/novartis_careers/job/insurgentes/global-finance-master-data-senior-specialist_req-10072223-1 | novartis | global finance master data senior specialist</t>
+          <t>match de keywords: finance | seniority alta | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7334756</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/stripe</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7334756 | stripe | head of global finance and accounting operations</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pflichtpraktikant (m/w/d) im Bereich Finance</t>
+          <t>Axial UK Deployment Project Manager (Finance)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Germany - Freiburg</t>
+          <t>Portugal - Lisboa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1331,7 +1426,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1356,7 +1451,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1369,62 +1464,73 @@
           <t>High</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>170-240k</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
         <is>
           <t>finance</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>https://pfizer.wd1.myworkdayjobs.com/PfizerCareers/job/Germany---Freiburg/Pflichtpraktikant--m-w-d--im-Bereich-Finance_4920391-1</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://pfizer.wd1.myworkdayjobs.com/PfizerCareers</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="b">
-        <v>1</v>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>https://pfizer.wd1.myworkdayjobs.com/pfizercareers/job/germany---freiburg/pflichtpraktikant--m-w-d--im-bereich-finance_4920391-1 | pfizer | pflichtpraktikant (m/w/d) im bereich finance</t>
+          <t>match de keywords: finance | seniority media-alta | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://astrazeneca.wd3.myworkdayjobs.com/Careers/job/Portugal---Lisboa/Axial-UK-Deployment-Project-Manager--Finance-_R-246388</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>https://astrazeneca.wd3.myworkdayjobs.com/Careers</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="Y10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>https://astrazeneca.wd3.myworkdayjobs.com/careers/job/portugal---lisboa/axial-uk-deployment-project-manager--finance-_r-246388 | astrazeneca | axial uk deployment project manager (finance)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>AstraZeneca Mexico</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Strategy &amp; Operations Business Partner</t>
+          <t>Axial UK Deployment Project Manager (Finance)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, San Fransisco, Seattle, Chicago, Remote in the US, Canada</t>
+          <t>Portugal - Lisboa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>remote</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1439,63 +1545,4370 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>LATAM</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>match de keywords: finance | seniority media-alta | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://astrazeneca.wd3.myworkdayjobs.com/Careers/job/Portugal---Lisboa/Axial-UK-Deployment-Project-Manager--Finance-_R-246388</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>https://astrazeneca.wd3.myworkdayjobs.com/Careers</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="Y11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>https://astrazeneca.wd3.myworkdayjobs.com/careers/job/portugal---lisboa/axial-uk-deployment-project-manager--finance-_r-246388 | astrazeneca mexico | axial uk deployment project manager (finance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Bristol-Myers Squibb</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Senior Manager, Finance, R&amp;D Global Drug Development</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2 Locations</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>match de keywords: finance | seniority media-alta | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://bristolmyerssquibb.wd5.myworkdayjobs.com/BMS/job/Princeton---NJ---US/Senior-Manager--Finance--R-D-Global-Drug-Development_R1599525</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>https://bristolmyerssquibb.wd5.myworkdayjobs.com/BMS</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>https://bristolmyerssquibb.wd5.myworkdayjobs.com/bms/job/princeton---nj---us/senior-manager--finance--r-d-global-drug-development_r1599525 | bristol-myers squibb | senior manager, finance, r&amp;d global drug development</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Coca-Cola FEMSA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Senior Manager, Operations Finance - Base &amp; Balanced Markets</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Singapore - Singapore</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>LATAM</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>match de keywords: finance | seniority media-alta | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://coke.wd1.myworkdayjobs.com/coca-cola-careers/job/Singapore---Singapore/Senior-Manager--Operations-Finance---Base---Balanced-Markets_R-135012</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>https://coke.wd1.myworkdayjobs.com/coca-cola-careers</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="Y13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>https://coke.wd1.myworkdayjobs.com/coca-cola-careers/job/singapore---singapore/senior-manager--operations-finance---base---balanced-markets_r-135012 | coca-cola femsa | senior manager, operations finance - base &amp; balanced markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Senior Manager, Finance Transformation</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote - USA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>11</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>greenhouse</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Fintech</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>200-300k</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Finance &amp; Accounting</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>finance, finance transformation</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>match de keywords: finance, finance transformation | seniority media-alta | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://www.coinbase.com/careers/positions/7430307?gh_jid=7430307</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/coinbase</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>https://www.coinbase.com/careers/positions/7430307?gh_jid=7430307 | coinbase | senior manager, finance transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Senior Product Manager, Enterprise Applications - Finance Systems</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Remote - USA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>11</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Enterprise Applications</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>match de keywords: finance | seniority media-alta | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://www.coinbase.com/careers/positions/7404427?gh_jid=7404427</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/coinbase</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>https://www.coinbase.com/careers/positions/7404427?gh_jid=7404427 | coinbase | senior product manager, enterprise applications - finance systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Dbt Labs</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Director, GTM Finance &amp; Strategy</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>US - Remote</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>11</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Finance &amp; Strategy</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Ejecutivo</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>match de keywords: finance | seniority alta | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/dbtlabsinc/jobs/4668459005</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/dbtlabsinc</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/dbtlabsinc/jobs/4668459005 | dbt labs | director, gtm finance &amp; strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Strategic Finance Manager</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>United States - Remote</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Accounting &amp; Finance</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>finance, strategic finance, finance manager</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>match fuerte de keywords: finance, strategic finance, finance manager | seniority media-alta | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=7706355</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=7706355 | instacart | strategic finance manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Strategic Finance Manager</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Canada - Remote (ON, AB, BC, or NS Only)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>11</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Accounting &amp; Finance</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>finance, strategic finance, finance manager</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>match fuerte de keywords: finance, strategic finance, finance manager | seniority media-alta | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=7705901</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=7705901 | instacart | strategic finance manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Senior Manager, People Business Partner - APJ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>11</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Employee Relations &amp; Compliance-159</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>business partner</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>match de keywords: business partner | seniority media-alta | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://www.okta.com/company/careers/opportunity/7685047?gh_jid=7685047</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/okta</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>https://www.okta.com/company/careers/opportunity/7685047?gh_jid=7685047 | okta | senior manager, people business partner - apj</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Affirm</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Finance/Analytics Quantitative Model Risk Manager</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Remote Canada</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Internal Audit</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>match de keywords: finance | seniority media-alta | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/6678708003</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/6678708003 | affirm | finance/analytics quantitative model risk manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Affirm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Finance/Analytics Quantitative Model Risk Manager</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Remote US</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Internal Audit</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>match de keywords: finance | seniority media-alta | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/6678706003</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/affirm</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/affirm/jobs/6678706003 | affirm | finance/analytics quantitative model risk manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Senior FP&amp;A Analyst, Corporate Finance</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Remote; Remote, Canada; Remote, US</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>finance, fp&amp;a, corporate finance</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>match fuerte de keywords: finance, fp&amp;a, corporate finance | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8347674002</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/gitlab</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8347674002 | gitlab | senior fp&amp;a analyst, corporate finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Grafana Labs</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Strategic Finance &amp; Analytics Manager | USA | Remote</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>United States (Remote)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>finance, strategic finance</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>match de keywords: finance, strategic finance | seniority media-alta | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/5811992004</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/grafanalabs</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/5811992004 | grafana labs | strategic finance &amp; analytics manager | usa | remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Senior Manager, FP&amp;A</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>fp&amp;a</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>match de keywords: fp&amp;a | seniority media-alta | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://navan.com/careers/openings?gh_jid=7536444</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/tripactions</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>https://navan.com/careers/openings?gh_jid=7536444 | navan | senior manager, fp&amp;a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sr Technology FP&amp;A Manager - Cloud Hosting</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Corporate Finance</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>fp&amp;a</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>match de keywords: fp&amp;a | seniority media-alta | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7363444</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/reddit</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/7363444 | reddit | sr technology fp&amp;a manager - cloud hosting</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sr. Manager, Sales Business Partner</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Sales Operations</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>business partner</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>match de keywords: business partner | seniority media-alta | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7639506</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/twilio</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7639506 | twilio | sr. manager, sales business partner</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Zilch</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Finance Director</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Ejecutivo</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>finance, finance director</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>match de keywords: finance, finance director | seniority alta | señal internacional/remota</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://www.payzilch.com/job/5795873004?gh_jid=5795873004</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/zilch</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="Y27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>https://www.payzilch.com/job/5795873004?gh_jid=5795873004 | zilch | finance director</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Zilch</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Senior Strategic Finance Manager</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>London, England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>finance, strategic finance, finance manager</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>match fuerte de keywords: finance, strategic finance, finance manager | seniority media-alta | señal internacional/remota</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://www.payzilch.com/job/5703899004?gh_jid=5703899004</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/zilch</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="Y28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>https://www.payzilch.com/job/5703899004?gh_jid=5703899004 | zilch | senior strategic finance manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HR Business Partner</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ireland - Finisklin</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>9</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>MedTech</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Principiante</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>business partner</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>match de keywords: business partner | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://abbott.wd5.myworkdayjobs.com/AbbottCareers/job/Ireland---Finisklin/HR-Business-Partner_31140580-1</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>https://abbott.wd5.myworkdayjobs.com/AbbottCareers</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>https://abbott.wd5.myworkdayjobs.com/abbottcareers/job/ireland---finisklin/hr-business-partner_31140580-1 | abbott | hr business partner</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Senior Recruitment Business Partner</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>9</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>business partner</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>match de keywords: business partner | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/adyen/jobs/7585548</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/adyen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="Y30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/adyen/jobs/7585548 | adyen | senior recruitment business partner</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Senior Recruitment Business Partner (Japan Market)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>9</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G31" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>business partner</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>match de keywords: business partner | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/adyen/jobs/7574410</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/adyen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="Y31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/adyen/jobs/7574410 | adyen | senior recruitment business partner (japan market)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Global People Business Partner</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>New York, US, New York</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>9</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>People &amp; Culture</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Principiante</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>business partner</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>match de keywords: business partner | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7595009003?gh_jid=7595009003</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/celonis</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="Y32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7595009003?gh_jid=7595009003 | celonis | global people business partner</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Global People Business Partner</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Raleigh, US, North Carolina</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>9</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>People &amp; Culture</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Principiante</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>business partner</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>match de keywords: business partner | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7584115003?gh_jid=7584115003</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/celonis</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="Y33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7584115003?gh_jid=7584115003 | celonis | global people business partner</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Financial Analyst, Corporate FP&amp;A</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Remote - USA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>9</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Finance &amp; Accounting</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Principiante</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>fp&amp;a</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>match de keywords: fp&amp;a | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://www.coinbase.com/careers/positions/7676111?gh_jid=7676111</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/coinbase</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>https://www.coinbase.com/careers/positions/7676111?gh_jid=7676111 | coinbase | financial analyst, corporate fp&amp;a</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sr. Analyst II, Finance Transformation (Remote)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>USA - Remote</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>9</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Principiante</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>finance, finance transformation</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>match de keywords: finance, finance transformation | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://crowdstrike.wd5.myworkdayjobs.com/crowdstrikecareers/job/USA---Remote/Sr-Analyst-II--Finance-Transformation--Remote-_R27107</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>https://crowdstrike.wd5.myworkdayjobs.com/crowdstrikecareers</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>https://crowdstrike.wd5.myworkdayjobs.com/crowdstrikecareers/job/usa---remote/sr-analyst-ii--finance-transformation--remote-_r27107 | crowdstrike | sr. analyst ii, finance transformation (remote)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FP&amp;A Analyst, Marketing</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Remote, Canada; Remote, US</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>9</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Principiante</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>fp&amp;a</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>match de keywords: fp&amp;a | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8393662002</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/gitlab</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8393662002 | gitlab | fp&amp;a analyst, marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>GitLab</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Senior People Business Partner</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Remote, Canada; Remote, United Kingdom; Remote, US</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>9</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>People Business Partners</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>business partner</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>match de keywords: business partner | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8428928002</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/gitlab</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8428928002 | gitlab | senior people business partner</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Scale AI</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Finance Fellow - Human Frontier Collective (UK)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>9</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Specialist</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Principiante</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>match de keywords: finance | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4613327005</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/scaleai</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y38" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/scaleai/jobs/4613327005 | scale ai | finance fellow - human frontier collective (uk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Strategy &amp; Operations Business Partner</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>New York, San Fransisco, Seattle, Chicago, Remote in the US, Canada</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>9</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
         <is>
           <t>2315 Marketing - Marketing Operations</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Principiante</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
         <is>
           <t>business partner</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>match de keywords: business partner | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
         <is>
           <t>https://stripe.com/jobs/search?gh_jid=7309571</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="b">
-        <v>1</v>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z39" t="inlineStr">
         <is>
           <t>https://stripe.com/jobs/search?gh_jid=7309571 | stripe | strategy &amp; operations business partner</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Stryker</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Senior Talent Acquisition Business Partner - Joint Replacement (Remote)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4 Locations</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>9</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>workday</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>MedTech</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>business partner</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>match de keywords: business partner | señal internacional/remota | empresa prioridad A</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Dallas-Texas/Senior-Talent-Acquisition-Business-Partner---Joint-Replacement--Remote-_R561035-1</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>https://stryker.wd1.myworkdayjobs.com/strykercareers/job/dallas-texas/senior-talent-acquisition-business-partner---joint-replacement--remote-_r561035-1 | stryker | senior talent acquisition business partner - joint replacement (remote)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Airtable</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Strategic Finance Analyst</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>San Francisco, CA; New York, NY; Remote - US</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>8</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G41" t="b">
+        <v>1</v>
+      </c>
+      <c r="H41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Principiante</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>finance, strategic finance</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>match de keywords: finance, strategic finance | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/airtable/jobs/8420850002</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/airtable</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y41" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/airtable/jobs/8420850002 | airtable | strategic finance analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Grafana Labs</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>People Business Partner | 12 Month Contract | Sydney or Melbourne | Remote</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>APAC (Remote)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>8</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G42" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Principiante</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>business partner</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>match de keywords: business partner | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/5762323004</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/grafanalabs</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y42" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/grafanalabs/jobs/5762323004 | grafana labs | people business partner | 12 month contract | sydney or melbourne | remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Finance Analyst (Strategic Finance - Ads)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>United States - Remote</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>8</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G43" t="b">
+        <v>1</v>
+      </c>
+      <c r="H43" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Accounting &amp; Finance</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Principiante</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>finance, strategic finance</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>match de keywords: finance, strategic finance | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=7624684</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y43" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=7624684 | instacart | finance analyst (strategic finance - ads)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Financial Analyst II — Strategic Finance (Fulfillment)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Canada - Remote</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>8</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G44" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Accounting &amp; Finance</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Principiante</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>finance, strategic finance</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>match de keywords: finance, strategic finance | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=7630251</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y44" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=7630251 | instacart | financial analyst ii — strategic finance (fulfillment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Financial Analyst II — Strategic Finance (Fulfillment)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>United States - Remote</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>8</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G45" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Accounting &amp; Finance</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Principiante</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>finance, strategic finance</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>match de keywords: finance, strategic finance | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=7630211</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y45" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=7630211 | instacart | financial analyst ii — strategic finance (fulfillment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Finance</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Canada - Remote (ON, AB, BC, or NS Only)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>8</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G46" t="b">
+        <v>1</v>
+      </c>
+      <c r="H46" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>match de keywords: finance | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=7688594</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/instacart</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y46" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=7688594 | instacart | senior data engineer, finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sr. People Success Business Partner</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>8</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G47" t="b">
+        <v>1</v>
+      </c>
+      <c r="H47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Principiante</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>business partner</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>match de keywords: business partner | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://navan.com/careers/openings?gh_jid=7306760</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/tripactions</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y47" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>https://navan.com/careers/openings?gh_jid=7306760 | navan | sr. people success business partner</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Pleo</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Senior Finance Business Partner</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>London, UK Remote</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>8</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G48" t="b">
+        <v>1</v>
+      </c>
+      <c r="H48" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>finance, business partner</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>match de keywords: finance, business partner | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://pleo.io/en/careers/jobs/7528504003?gh_jid=7528504003</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/pleo</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="Y48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>https://pleo.io/en/careers/jobs/7528504003?gh_jid=7528504003 | pleo | senior finance business partner</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SumUp</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Senior Sales Operations Business Partner - Retail</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>8</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G49" t="b">
+        <v>1</v>
+      </c>
+      <c r="H49" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Sales Operations</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>business partner</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>match de keywords: business partner | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://sumup.com/careers/positions/8408767002?gh_jid=8408767002</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/sumup</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="Y49" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>https://sumup.com/careers/positions/8408767002?gh_jid=8408767002 | sumup | senior sales operations business partner - retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Deal Desk Finance Analyst</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Remote - US</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>8</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G50" t="b">
+        <v>1</v>
+      </c>
+      <c r="H50" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Twilio.org</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Principiante</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>match de keywords: finance | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7492664</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/twilio</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y50" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7492664 | twilio | deal desk finance analyst</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Senior Enablement Business Partner, Customer Value</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Remote - Canada</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>8</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G51" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Sales Operations</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Intermedio</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>business partner</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>match de keywords: business partner | señal internacional/remota | empresa prioridad B</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7599086</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/twilio</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Y51" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/7599086 | twilio | senior enablement business partner, customer value</t>
         </is>
       </c>
     </row>
